--- a/fixtures/report_spillref.xlsx
+++ b/fixtures/report_spillref.xlsx
@@ -555,15 +555,15 @@
         <x:v>Food</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:f>COUNTA(Summary!D2#)</x:f>
+        <x:f>COUNTA(_xlfn.ANCHORARRAY(Summary!D2))</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:f>COUNTIF(Summary!D2#, "Food")</x:f>
+        <x:f>COUNTIF(_xlfn.ANCHORARRAY(Summary!D2), "Food")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H2" s="0" t="str">
-        <x:f>_xlfn.TEXTJOIN(", ", TRUE, Summary!D2#)</x:f>
+        <x:f>_xlfn.TEXTJOIN(", ", TRUE, _xlfn.ANCHORARRAY(Summary!D2))</x:f>
         <x:v>Food, Rent, Supplies, Travel</x:v>
       </x:c>
     </x:row>
